--- a/research/traditional_assets/database/data/kuwait/kuwait_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_financial_svcs_non_bank_insurance.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.205</v>
+        <v>-0.00459</v>
       </c>
       <c r="E2">
-        <v>0.599</v>
+        <v>0.00697</v>
       </c>
       <c r="G2">
-        <v>0.1762370437292885</v>
+        <v>0.4977739787769715</v>
       </c>
       <c r="H2">
-        <v>0.1762370437292885</v>
+        <v>0.4977739787769715</v>
       </c>
       <c r="I2">
-        <v>0.3091965259372453</v>
+        <v>0.2705077110053896</v>
       </c>
       <c r="J2">
-        <v>0.3072671895172859</v>
+        <v>0.2678178684572794</v>
       </c>
       <c r="K2">
-        <v>346.11</v>
+        <v>192.376</v>
       </c>
       <c r="L2">
-        <v>0.610731338911691</v>
+        <v>0.4080353109112158</v>
       </c>
       <c r="M2">
-        <v>98.27500000000001</v>
+        <v>166.74</v>
       </c>
       <c r="N2">
-        <v>0.02777228282371559</v>
+        <v>0.057177148343735</v>
       </c>
       <c r="O2">
-        <v>0.2839415214816099</v>
+        <v>0.8667401339044372</v>
       </c>
       <c r="P2">
-        <v>66.22199999999999</v>
+        <v>126.01</v>
       </c>
       <c r="Q2">
-        <v>0.01871418074944893</v>
+        <v>0.04321034222618476</v>
       </c>
       <c r="R2">
-        <v>0.1913322354164861</v>
+        <v>0.6550193371314509</v>
       </c>
       <c r="S2">
-        <v>32.053</v>
+        <v>40.73</v>
       </c>
       <c r="T2">
-        <v>0.326156194352582</v>
+        <v>0.2442725200911599</v>
       </c>
       <c r="U2">
-        <v>532.356</v>
+        <v>447.428</v>
       </c>
       <c r="V2">
-        <v>0.1504425479002996</v>
+        <v>0.1534284342637679</v>
       </c>
       <c r="W2">
-        <v>0.1354723707664884</v>
+        <v>0.05144392209536602</v>
       </c>
       <c r="X2">
-        <v>0.02522212271687906</v>
+        <v>0.05217308890678861</v>
       </c>
       <c r="Y2">
-        <v>0.1102502480496094</v>
+        <v>-0.0007291668114225922</v>
       </c>
       <c r="Z2">
-        <v>0.2019062874423234</v>
+        <v>0.1812051569420551</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02519176271974682</v>
+        <v>0.05157891833194144</v>
       </c>
       <c r="AC2">
-        <v>-0.02695042874992195</v>
+        <v>-0.05157891833194144</v>
       </c>
       <c r="AD2">
-        <v>688.97</v>
+        <v>754.6800000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>688.97</v>
+        <v>754.6800000000001</v>
       </c>
       <c r="AG2">
-        <v>156.614</v>
+        <v>307.2520000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1629706900181428</v>
+        <v>0.2055855816588938</v>
       </c>
       <c r="AI2">
-        <v>0.1915577464710413</v>
+        <v>0.2115976649899904</v>
       </c>
       <c r="AJ2">
-        <v>0.04238293100210164</v>
+        <v>0.0953176904759246</v>
       </c>
       <c r="AK2">
-        <v>0.05110899209415225</v>
+        <v>0.09850497827614688</v>
       </c>
       <c r="AL2">
-        <v>5.926</v>
+        <v>7.315</v>
       </c>
       <c r="AM2">
-        <v>-10.254</v>
+        <v>2.865</v>
       </c>
       <c r="AN2">
-        <v>3.03993116837275</v>
+        <v>4.253012183988369</v>
       </c>
       <c r="AO2">
-        <v>29.56901788727641</v>
+        <v>17.43485987696514</v>
       </c>
       <c r="AP2">
-        <v>0.6910254147546772</v>
+        <v>1.731523956583975</v>
       </c>
       <c r="AQ2">
-        <v>-17.08855080944022</v>
+        <v>44.5151832460733</v>
       </c>
     </row>
     <row r="3">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.3831231813773036</v>
+        <v>0.5436893203883495</v>
       </c>
       <c r="H3">
-        <v>0.3831231813773036</v>
+        <v>0.5436893203883495</v>
       </c>
       <c r="I3">
-        <v>0.5664403491755577</v>
+        <v>0.6663724624889673</v>
       </c>
       <c r="J3">
-        <v>0.5664403491755577</v>
+        <v>0.6575789275723454</v>
       </c>
       <c r="K3">
-        <v>52</v>
+        <v>62.2</v>
       </c>
       <c r="L3">
-        <v>0.504364694471387</v>
+        <v>0.5489849955869374</v>
       </c>
       <c r="M3">
-        <v>26.2</v>
+        <v>40.8</v>
       </c>
       <c r="N3">
-        <v>0.01954057279236277</v>
+        <v>0.03036844064011909</v>
       </c>
       <c r="O3">
-        <v>0.5038461538461538</v>
+        <v>0.6559485530546623</v>
       </c>
       <c r="P3">
-        <v>26.2</v>
+        <v>40.8</v>
       </c>
       <c r="Q3">
-        <v>0.01954057279236277</v>
+        <v>0.03036844064011909</v>
       </c>
       <c r="R3">
-        <v>0.5038461538461538</v>
+        <v>0.6559485530546623</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>122.3</v>
+        <v>17.5</v>
       </c>
       <c r="V3">
-        <v>0.09121420047732696</v>
+        <v>0.01302567919612951</v>
       </c>
       <c r="W3">
-        <v>0.3266331658291458</v>
+        <v>0.3322649572649573</v>
       </c>
       <c r="X3">
-        <v>0.02432390685401275</v>
+        <v>0.05007711512095263</v>
       </c>
       <c r="Y3">
-        <v>0.302309258975133</v>
+        <v>0.2821878421440047</v>
       </c>
       <c r="Z3">
-        <v>1.2193968066233</v>
+        <v>3.058855291576676</v>
       </c>
       <c r="AA3">
-        <v>0.6907155529272621</v>
+        <v>2.011438782233984</v>
       </c>
       <c r="AB3">
-        <v>0.02434319587200605</v>
+        <v>0.05007151701315758</v>
       </c>
       <c r="AC3">
-        <v>0.666372357055256</v>
+        <v>1.961367265220827</v>
       </c>
       <c r="AD3">
-        <v>3.64</v>
+        <v>2.97</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.64</v>
+        <v>2.97</v>
       </c>
       <c r="AG3">
-        <v>-118.66</v>
+        <v>-14.53</v>
       </c>
       <c r="AH3">
-        <v>0.002707446966766832</v>
+        <v>0.002205767673991994</v>
       </c>
       <c r="AI3">
-        <v>0.01145951391512404</v>
+        <v>0.008782564982109589</v>
       </c>
       <c r="AJ3">
-        <v>-0.09709198618816176</v>
+        <v>-0.01093327915603813</v>
       </c>
       <c r="AK3">
-        <v>-0.6074536705231903</v>
+        <v>-0.04531137929959148</v>
       </c>
       <c r="AL3">
-        <v>0.146</v>
+        <v>0.129</v>
       </c>
       <c r="AM3">
-        <v>-3.314</v>
+        <v>-4.321</v>
       </c>
       <c r="AN3">
-        <v>0.06026490066225166</v>
+        <v>0.03837209302325582</v>
       </c>
       <c r="AO3">
-        <v>400</v>
+        <v>585.2713178294573</v>
       </c>
       <c r="AP3">
-        <v>-1.964569536423841</v>
+        <v>-0.1877260981912144</v>
       </c>
       <c r="AQ3">
-        <v>-17.6222088111044</v>
+        <v>-17.4728072205508</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kuwait Investment Company K.S.C.P. (KWSE:KINV)</t>
+          <t>A'ayan Leasing and Investment Company K.S.C.P. (KWSE:AAYAN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,121 +850,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.212</v>
+        <v>-0.00459</v>
       </c>
       <c r="E4">
-        <v>0.745</v>
+        <v>-0.0449</v>
       </c>
       <c r="G4">
-        <v>0.1417322834645669</v>
+        <v>0.8037676609105181</v>
       </c>
       <c r="H4">
-        <v>0.1417322834645669</v>
+        <v>0.8037676609105181</v>
       </c>
       <c r="I4">
-        <v>0.658267716535433</v>
+        <v>0.4018838304552591</v>
       </c>
       <c r="J4">
-        <v>0.6533041043079776</v>
+        <v>0.3797009953691982</v>
       </c>
       <c r="K4">
-        <v>82.5</v>
+        <v>23.2</v>
       </c>
       <c r="L4">
-        <v>0.6496062992125984</v>
+        <v>0.3642072213500785</v>
       </c>
       <c r="M4">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="N4">
-        <v>0.04134672179562907</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="O4">
-        <v>0.2545454545454545</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="P4">
-        <v>21</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.04134672179562907</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.2545454545454545</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>63.1</v>
+        <v>52.5</v>
       </c>
       <c r="V4">
-        <v>0.1242370545382949</v>
+        <v>0.1822916666666667</v>
       </c>
       <c r="W4">
-        <v>0.245462659922642</v>
+        <v>0.08140350877192983</v>
       </c>
       <c r="X4">
-        <v>0.02522212271687906</v>
+        <v>0.05052769898244668</v>
       </c>
       <c r="Y4">
-        <v>0.220240537205763</v>
+        <v>0.03087580978948315</v>
       </c>
       <c r="Z4">
-        <v>0.3835699184536394</v>
+        <v>0.2979447890064453</v>
       </c>
       <c r="AA4">
-        <v>0.2505878020148389</v>
+        <v>0.113129932950813</v>
       </c>
       <c r="AB4">
-        <v>0.02519176271974682</v>
+        <v>0.05069481330964262</v>
       </c>
       <c r="AC4">
-        <v>0.2253960392950921</v>
+        <v>0.06243511964117038</v>
       </c>
       <c r="AD4">
-        <v>59.7</v>
+        <v>14.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>59.7</v>
+        <v>14.2</v>
       </c>
       <c r="AG4">
-        <v>-3.399999999999999</v>
+        <v>-38.3</v>
       </c>
       <c r="AH4">
-        <v>0.1051797040169133</v>
+        <v>0.04698874917273329</v>
       </c>
       <c r="AI4">
-        <v>0.1031088082901555</v>
+        <v>0.04138735062663947</v>
       </c>
       <c r="AJ4">
-        <v>-0.006739345887016845</v>
+        <v>-0.1533840608730477</v>
       </c>
       <c r="AK4">
-        <v>-0.00659042450087226</v>
+        <v>-0.1317962835512732</v>
       </c>
       <c r="AL4">
-        <v>5.73</v>
+        <v>0.026</v>
       </c>
       <c r="AM4">
-        <v>4.31</v>
+        <v>0.026</v>
       </c>
       <c r="AN4">
-        <v>0.5875984251968505</v>
+        <v>0.2577132486388384</v>
       </c>
       <c r="AO4">
-        <v>14.58987783595113</v>
+        <v>984.6153846153848</v>
       </c>
       <c r="AP4">
-        <v>-0.03346456692913385</v>
+        <v>-0.6950998185117967</v>
       </c>
       <c r="AQ4">
-        <v>19.39675174013921</v>
+        <v>984.6153846153848</v>
       </c>
     </row>
     <row r="5">
@@ -983,35 +983,32 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.434</v>
-      </c>
       <c r="G5">
-        <v>-0.01705882352941177</v>
+        <v>0.492</v>
       </c>
       <c r="H5">
-        <v>-0.01705882352941177</v>
+        <v>0.492</v>
       </c>
       <c r="I5">
-        <v>0.4338235294117647</v>
+        <v>0.2488</v>
       </c>
       <c r="J5">
-        <v>0.4338235294117647</v>
+        <v>0.2466569044414536</v>
       </c>
       <c r="K5">
-        <v>-12.4</v>
+        <v>7.66</v>
       </c>
       <c r="L5">
-        <v>-0.4558823529411765</v>
+        <v>0.3064</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>8.32</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.08648648648648649</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.086161879895561</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1020,79 +1017,82 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>8.32</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="V5">
-        <v>0.15086782376502</v>
+        <v>0.237006237006237</v>
       </c>
       <c r="W5">
-        <v>-0.07735495945102931</v>
+        <v>0.05144392209536602</v>
       </c>
       <c r="X5">
-        <v>0.02448177903588925</v>
+        <v>0.05064075996640922</v>
       </c>
       <c r="Y5">
-        <v>-0.1018367384869186</v>
+        <v>0.0008031621289567997</v>
       </c>
       <c r="Z5">
-        <v>0.1868131868131868</v>
+        <v>0.2053050833538638</v>
       </c>
       <c r="AA5">
-        <v>0.08104395604395605</v>
+        <v>0.05063991632615864</v>
       </c>
       <c r="AB5">
-        <v>0.02457975317058848</v>
+        <v>0.05083910710935242</v>
       </c>
       <c r="AC5">
-        <v>0.05646420287336756</v>
+        <v>-0.0001991907831937756</v>
       </c>
       <c r="AD5">
-        <v>3.43</v>
+        <v>5.88</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3.43</v>
+        <v>5.88</v>
       </c>
       <c r="AG5">
-        <v>-19.17</v>
+        <v>-16.92</v>
       </c>
       <c r="AH5">
-        <v>0.02238465052535404</v>
+        <v>0.05760188087774295</v>
       </c>
       <c r="AI5">
-        <v>0.02265072971009708</v>
+        <v>0.04236921746649373</v>
       </c>
       <c r="AJ5">
-        <v>-0.1467503636224451</v>
+        <v>-0.2134207870837538</v>
       </c>
       <c r="AK5">
-        <v>-0.1488007451680509</v>
+        <v>-0.1458872219348163</v>
       </c>
       <c r="AL5">
-        <v>0.05</v>
+        <v>0.193</v>
       </c>
       <c r="AM5">
-        <v>0.05</v>
+        <v>0.193</v>
       </c>
       <c r="AN5">
-        <v>0.2598484848484849</v>
+        <v>0.760672703751617</v>
       </c>
       <c r="AO5">
-        <v>236</v>
+        <v>32.2279792746114</v>
       </c>
       <c r="AP5">
-        <v>-1.452272727272727</v>
+        <v>-2.188874514877102</v>
       </c>
       <c r="AQ5">
-        <v>236</v>
+        <v>32.2279792746114</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A'ayan Leasing and Investment Company K.S.C.P. (KWSE:AAYAN)</t>
+          <t>Kuwait Investment Company K.S.C.P. (KWSE:KINV)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,118 +1112,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0443</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="E6">
-        <v>0.7809999999999999</v>
+        <v>-0.321</v>
       </c>
       <c r="G6">
-        <v>0.8305709023941069</v>
+        <v>1.822742474916388</v>
       </c>
       <c r="H6">
-        <v>0.8305709023941069</v>
+        <v>1.822742474916388</v>
       </c>
       <c r="I6">
-        <v>0.4364640883977901</v>
+        <v>0.3193979933110369</v>
       </c>
       <c r="J6">
-        <v>0.4248705110497237</v>
+        <v>0.3162932306944938</v>
       </c>
       <c r="K6">
-        <v>100.5</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="L6">
-        <v>1.850828729281768</v>
+        <v>0.1416387959866221</v>
       </c>
       <c r="M6">
-        <v>30.2</v>
+        <v>44</v>
       </c>
       <c r="N6">
-        <v>0.08120462489916644</v>
+        <v>0.1620029455081001</v>
       </c>
       <c r="O6">
-        <v>0.3004975124378109</v>
+        <v>5.194805194805195</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>44</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.1620029455081001</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>5.194805194805195</v>
       </c>
       <c r="S6">
-        <v>30.2</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>86.2</v>
+        <v>64</v>
       </c>
       <c r="V6">
-        <v>0.2317827372949718</v>
+        <v>0.235640648011782</v>
       </c>
       <c r="W6">
-        <v>0.4774346793349168</v>
+        <v>0.02060827250608273</v>
       </c>
       <c r="X6">
-        <v>0.02462447989344543</v>
+        <v>0.05217308890678861</v>
       </c>
       <c r="Y6">
-        <v>0.4528101994414714</v>
+        <v>-0.03156481640070588</v>
       </c>
       <c r="Z6">
-        <v>0.1016846315757935</v>
+        <v>0.1467124631992149</v>
       </c>
       <c r="AA6">
-        <v>0.04320280138351024</v>
+        <v>0.04640415896842671</v>
       </c>
       <c r="AB6">
-        <v>0.02479178980522422</v>
+        <v>0.05251935430579009</v>
       </c>
       <c r="AC6">
-        <v>0.01841101157828602</v>
+        <v>-0.006115195337363384</v>
       </c>
       <c r="AD6">
-        <v>15.3</v>
+        <v>60.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>15.3</v>
+        <v>60.1</v>
       </c>
       <c r="AG6">
-        <v>-70.90000000000001</v>
+        <v>-3.899999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.03951446280991736</v>
+        <v>0.1811878203195658</v>
       </c>
       <c r="AI6">
-        <v>0.0446064139941691</v>
+        <v>0.1133962264150943</v>
       </c>
       <c r="AJ6">
-        <v>-0.2355481727574751</v>
+        <v>-0.01456854688083675</v>
       </c>
       <c r="AK6">
-        <v>-0.2760903426791278</v>
+        <v>-0.008369098712446349</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="AM6">
-        <v>-11.3</v>
+        <v>6.79</v>
       </c>
       <c r="AN6">
-        <v>0.2849162011173184</v>
+        <v>1.664819944598338</v>
+      </c>
+      <c r="AO6">
+        <v>2.812960235640648</v>
       </c>
       <c r="AP6">
-        <v>-1.320297951582868</v>
+        <v>-0.1080332409972299</v>
       </c>
       <c r="AQ6">
-        <v>-2.097345132743363</v>
+        <v>2.812960235640648</v>
       </c>
     </row>
     <row r="7">
@@ -1234,7 +1237,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arzan Financial Group for Financing and Investment - KPSC (KWSE:ARZAN)</t>
+          <t>Al Madar Finance and Investment Company K.S.C.P. (KWSE:MADAR)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1243,34 +1246,34 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.122</v>
+        <v>-0.0808</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.2354260089686099</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.2354260089686099</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.4170403587443947</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.4170403587443947</v>
       </c>
       <c r="K7">
-        <v>17.2</v>
+        <v>1.33</v>
       </c>
       <c r="L7">
-        <v>0.3747276688453159</v>
+        <v>0.2982062780269059</v>
       </c>
       <c r="M7">
-        <v>1.19</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.002859889449651526</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.06918604651162791</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1282,67 +1285,76 @@
         <v>-0</v>
       </c>
       <c r="S7">
-        <v>1.19</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>25.3</v>
+        <v>0.577</v>
       </c>
       <c r="V7">
-        <v>0.06080269166065849</v>
+        <v>0.007493506493506493</v>
       </c>
       <c r="W7">
-        <v>0.05320136096504794</v>
+        <v>0.01867977528089888</v>
       </c>
       <c r="X7">
-        <v>0.02565807999115152</v>
+        <v>0.05046973096762462</v>
       </c>
       <c r="Y7">
-        <v>0.02754328097389642</v>
+        <v>-0.03178995568672575</v>
       </c>
       <c r="Z7">
-        <v>0.125</v>
+        <v>0.06320861678004534</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.02636054421768708</v>
       </c>
       <c r="AB7">
-        <v>0.02613075346534312</v>
+        <v>0.05034824766545265</v>
       </c>
       <c r="AC7">
-        <v>-0.02613075346534312</v>
+        <v>-0.02398770344776557</v>
       </c>
       <c r="AD7">
-        <v>72.09999999999999</v>
+        <v>3.33</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>72.09999999999999</v>
+        <v>3.33</v>
       </c>
       <c r="AG7">
-        <v>46.8</v>
+        <v>2.753</v>
       </c>
       <c r="AH7">
-        <v>0.1476853748463744</v>
+        <v>0.04145400224075688</v>
       </c>
       <c r="AI7">
-        <v>0.1218934911242603</v>
+        <v>0.04181841014692955</v>
       </c>
       <c r="AJ7">
-        <v>0.101101749837978</v>
+        <v>0.03451907765225132</v>
       </c>
       <c r="AK7">
-        <v>0.08265630519251148</v>
+        <v>0.0348247378341113</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.177</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.177</v>
+      </c>
+      <c r="AN7">
+        <v>1.790322580645161</v>
+      </c>
+      <c r="AO7">
+        <v>10.50847457627119</v>
+      </c>
+      <c r="AP7">
+        <v>1.48010752688172</v>
+      </c>
+      <c r="AQ7">
+        <v>10.50847457627119</v>
       </c>
     </row>
     <row r="8">
@@ -1353,7 +1365,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Al Manar Financing and Leasing Company K.S.C. (Public) (KWSE:ALMANAR)</t>
+          <t>Arzan Financial Group for Financing and Investment - KPSC (KWSE:ARZAN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1361,6 +1373,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>0.262</v>
+      </c>
+      <c r="E8">
+        <v>0.5820000000000001</v>
+      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -1374,85 +1392,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>-1.84</v>
+        <v>35.5</v>
       </c>
       <c r="L8">
-        <v>-0.3948497854077253</v>
+        <v>0.5599369085173501</v>
       </c>
       <c r="M8">
-        <v>0.769</v>
+        <v>8.91</v>
       </c>
       <c r="N8">
-        <v>0.01124269005847953</v>
+        <v>0.02961116650049851</v>
       </c>
       <c r="O8">
-        <v>-0.4179347826086957</v>
+        <v>0.2509859154929577</v>
       </c>
       <c r="P8">
-        <v>0.106</v>
+        <v>5.8</v>
       </c>
       <c r="Q8">
-        <v>0.001549707602339181</v>
+        <v>0.01927550681289465</v>
       </c>
       <c r="R8">
-        <v>-0.05760869565217391</v>
+        <v>0.1633802816901408</v>
       </c>
       <c r="S8">
-        <v>0.663</v>
+        <v>3.11</v>
       </c>
       <c r="T8">
-        <v>0.8621586475942783</v>
+        <v>0.3490460157126824</v>
       </c>
       <c r="U8">
-        <v>13.5</v>
+        <v>26</v>
       </c>
       <c r="V8">
-        <v>0.1973684210526316</v>
+        <v>0.08640744433366568</v>
       </c>
       <c r="W8">
-        <v>-0.01789883268482491</v>
+        <v>0.08971443012383119</v>
       </c>
       <c r="X8">
-        <v>0.02598377293389102</v>
+        <v>0.05269189533180595</v>
       </c>
       <c r="Y8">
-        <v>-0.04388260561871593</v>
+        <v>0.03702253479202524</v>
       </c>
       <c r="Z8">
-        <v>0.04317213266629609</v>
+        <v>0.1432768361581921</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.02695042874992195</v>
+        <v>0.05157891833194144</v>
       </c>
       <c r="AC8">
-        <v>-0.02695042874992195</v>
+        <v>-0.05157891833194144</v>
       </c>
       <c r="AD8">
-        <v>14.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>14.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AG8">
-        <v>1.199999999999999</v>
+        <v>56.90000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.1768953068592057</v>
+        <v>0.2159979155810318</v>
       </c>
       <c r="AI8">
-        <v>0.1261802575107296</v>
+        <v>0.1404846636163362</v>
       </c>
       <c r="AJ8">
-        <v>0.01724137931034482</v>
+        <v>0.1590273896031303</v>
       </c>
       <c r="AK8">
-        <v>0.0116504854368932</v>
+        <v>0.1008686403120014</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1469,7 +1487,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kuwait Finance and Investment Company K.S.C. (Public) (KWSE:KFIC)</t>
+          <t>Al Manar Financing and Leasing Company K.S.C. (Public) (KWSE:ALMANAR)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1477,12 +1495,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.267</v>
-      </c>
-      <c r="E9">
-        <v>0.599</v>
-      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1496,82 +1508,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>17</v>
+        <v>4.07</v>
       </c>
       <c r="L9">
-        <v>0.4533333333333333</v>
+        <v>0.5012315270935962</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>13.41</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.2655445544554456</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>3.294840294840295</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.002178217821782178</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.02702702702702703</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>13.3</v>
+      </c>
+      <c r="T9">
+        <v>0.9917971662938107</v>
       </c>
       <c r="U9">
-        <v>19.6</v>
+        <v>17.1</v>
       </c>
       <c r="V9">
-        <v>0.2212189616252822</v>
+        <v>0.3386138613861386</v>
       </c>
       <c r="W9">
-        <v>0.1375404530744337</v>
+        <v>0.03998035363457761</v>
       </c>
       <c r="X9">
-        <v>0.02626265293329415</v>
+        <v>0.05352302462826188</v>
       </c>
       <c r="Y9">
-        <v>0.1112778001411395</v>
+        <v>-0.01354267099368427</v>
       </c>
       <c r="Z9">
-        <v>0.2884615384615384</v>
+        <v>0.07883495145631067</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.02730166192389126</v>
+        <v>0.05367228391912036</v>
       </c>
       <c r="AC9">
-        <v>-0.02730166192389126</v>
+        <v>-0.05367228391912036</v>
       </c>
       <c r="AD9">
-        <v>22.2</v>
+        <v>18.3</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>22.2</v>
+        <v>18.3</v>
       </c>
       <c r="AG9">
-        <v>2.599999999999998</v>
+        <v>1.199999999999999</v>
       </c>
       <c r="AH9">
-        <v>0.2003610108303249</v>
+        <v>0.2659883720930233</v>
       </c>
       <c r="AI9">
-        <v>0.132300357568534</v>
+        <v>0.1716697936210131</v>
       </c>
       <c r="AJ9">
-        <v>0.02850877192982454</v>
+        <v>0.02321083172147</v>
       </c>
       <c r="AK9">
-        <v>0.0175438596491228</v>
+        <v>0.01340782122905027</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1588,7 +1603,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Commercial Facilities Company S.A.K.P. (KWSE:FACIL)</t>
+          <t>KAMCO Investment Company K.S.C.P. (KWSE:KAMCO)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1597,10 +1612,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.154</v>
+        <v>0.224</v>
       </c>
       <c r="E10">
-        <v>0.218</v>
+        <v>0.338</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1615,28 +1630,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>70.5</v>
+        <v>19.1</v>
       </c>
       <c r="L10">
-        <v>0.8216783216783217</v>
+        <v>0.2630853994490359</v>
       </c>
       <c r="M10">
-        <v>18.8</v>
+        <v>10.8</v>
       </c>
       <c r="N10">
-        <v>0.05436668594563331</v>
+        <v>0.09391304347826088</v>
       </c>
       <c r="O10">
-        <v>0.2666666666666667</v>
+        <v>0.5654450261780105</v>
       </c>
       <c r="P10">
-        <v>18.8</v>
+        <v>10.8</v>
       </c>
       <c r="Q10">
-        <v>0.05436668594563331</v>
+        <v>0.09391304347826088</v>
       </c>
       <c r="R10">
-        <v>0.2666666666666667</v>
+        <v>0.5654450261780105</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1645,55 +1660,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>74.59999999999999</v>
+        <v>101.6</v>
       </c>
       <c r="V10">
-        <v>0.2157316367842683</v>
+        <v>0.8834782608695652</v>
       </c>
       <c r="W10">
-        <v>0.149332768481254</v>
+        <v>0.09720101781170484</v>
       </c>
       <c r="X10">
-        <v>0.03219054160793738</v>
+        <v>0.06211942237766437</v>
       </c>
       <c r="Y10">
-        <v>0.1171422268733166</v>
+        <v>0.03508159543404048</v>
       </c>
       <c r="Z10">
-        <v>0.1085114455545719</v>
+        <v>0.3007456503728252</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.03181788992810567</v>
+        <v>0.05398813018715677</v>
       </c>
       <c r="AC10">
-        <v>-0.03181788992810567</v>
+        <v>-0.05398813018715677</v>
       </c>
       <c r="AD10">
-        <v>348.7</v>
+        <v>145</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>348.7</v>
+        <v>145</v>
       </c>
       <c r="AG10">
-        <v>274.1</v>
+        <v>43.40000000000001</v>
       </c>
       <c r="AH10">
-        <v>0.5020878329733621</v>
+        <v>0.5576923076923077</v>
       </c>
       <c r="AI10">
-        <v>0.3971073909577497</v>
+        <v>0.4087961657738934</v>
       </c>
       <c r="AJ10">
-        <v>0.4421680916276818</v>
+        <v>0.273989898989899</v>
       </c>
       <c r="AK10">
-        <v>0.3411325451151214</v>
+        <v>0.1714737258000791</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1710,7 +1725,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KAMCO Investment Company K.S.C.P. (KWSE:KAMCO)</t>
+          <t>Commercial Facilities Company S.A.K.P. (KWSE:FACIL)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1719,10 +1734,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.247</v>
+        <v>0.0064</v>
       </c>
       <c r="E11">
-        <v>0.262</v>
+        <v>0.00697</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1737,28 +1752,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>22.8</v>
+        <v>33.1</v>
       </c>
       <c r="L11">
-        <v>0.287515762925599</v>
+        <v>0.7164502164502164</v>
       </c>
       <c r="M11">
-        <v>0.116</v>
+        <v>24.5</v>
       </c>
       <c r="N11">
-        <v>0.0007945205479452055</v>
+        <v>0.08265856950067477</v>
       </c>
       <c r="O11">
-        <v>0.005087719298245614</v>
+        <v>0.7401812688821752</v>
       </c>
       <c r="P11">
-        <v>0.116</v>
+        <v>24.5</v>
       </c>
       <c r="Q11">
-        <v>0.0007945205479452055</v>
+        <v>0.08265856950067477</v>
       </c>
       <c r="R11">
-        <v>0.005087719298245614</v>
+        <v>0.7401812688821752</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1767,55 +1782,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>104.3</v>
+        <v>120.7</v>
       </c>
       <c r="V11">
-        <v>0.7143835616438357</v>
+        <v>0.4072199730094467</v>
       </c>
       <c r="W11">
-        <v>0.1354723707664884</v>
+        <v>0.0625354241450973</v>
       </c>
       <c r="X11">
-        <v>0.03229638832824656</v>
+        <v>0.06279012907143083</v>
       </c>
       <c r="Y11">
-        <v>0.1031759824382418</v>
+        <v>-0.0002547049263335321</v>
       </c>
       <c r="Z11">
-        <v>0.3388888888888889</v>
+        <v>0.05750560119492159</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.03186776640483234</v>
+        <v>0.05408191999251287</v>
       </c>
       <c r="AC11">
-        <v>-0.03186776640483234</v>
+        <v>-0.05408191999251287</v>
       </c>
       <c r="AD11">
-        <v>149.2</v>
+        <v>394.5</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>149.2</v>
+        <v>394.5</v>
       </c>
       <c r="AG11">
-        <v>44.89999999999999</v>
+        <v>273.8</v>
       </c>
       <c r="AH11">
-        <v>0.505420054200542</v>
+        <v>0.5709943551888841</v>
       </c>
       <c r="AI11">
-        <v>0.4159464733760803</v>
+        <v>0.4355266063148598</v>
       </c>
       <c r="AJ11">
-        <v>0.2352016762702986</v>
+        <v>0.4801823921431077</v>
       </c>
       <c r="AK11">
-        <v>0.1764937106918239</v>
+        <v>0.3487453827537894</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1832,7 +1847,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Al Madar Finance and Investment Company K.S.C. (Public) (KWSE:MADAR)</t>
+          <t>KFIC Invest (K.S.C.P) (KWSE:KFIC)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1841,25 +1856,25 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.4370000000000001</v>
+        <v>-0.0127</v>
       </c>
       <c r="G12">
-        <v>-2.665198237885462</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>-2.665198237885462</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>-3.700440528634361</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>-3.700440528634361</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>-1.01</v>
+        <v>-2.17</v>
       </c>
       <c r="L12">
-        <v>-2.224669603524229</v>
+        <v>-0.1561151079136691</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1883,67 +1898,61 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0.64</v>
+        <v>24.5</v>
       </c>
       <c r="V12">
-        <v>0.007862407862407862</v>
+        <v>0.3746177370030581</v>
       </c>
       <c r="W12">
-        <v>-0.01438746438746439</v>
+        <v>-0.01519607843137255</v>
       </c>
       <c r="X12">
-        <v>0.02430267097692251</v>
+        <v>0.05407902538459734</v>
       </c>
       <c r="Y12">
-        <v>-0.0386901353643869</v>
+        <v>-0.06927510381596989</v>
       </c>
       <c r="Z12">
-        <v>0.006901793858315597</v>
+        <v>0.09559834938101788</v>
       </c>
       <c r="AA12">
-        <v>-0.02553967771359076</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.02430267097692251</v>
+        <v>0.05503668518547522</v>
       </c>
       <c r="AC12">
-        <v>-0.04984234869051327</v>
+        <v>-0.05503668518547522</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="AG12">
-        <v>-0.64</v>
+        <v>3</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.2960172228202368</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.1672749391727494</v>
       </c>
       <c r="AJ12">
-        <v>-0.0079247152055473</v>
+        <v>0.04385964912280702</v>
       </c>
       <c r="AK12">
-        <v>-0.008348552048004174</v>
+        <v>0.02144388849177984</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>-0</v>
-      </c>
-      <c r="AP12">
-        <v>0.3832335329341318</v>
       </c>
     </row>
     <row r="13">
@@ -1962,26 +1971,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.205</v>
-      </c>
       <c r="G13">
-        <v>-0.7000000000000001</v>
+        <v>-0.4701718907987867</v>
       </c>
       <c r="H13">
-        <v>-0.7000000000000001</v>
+        <v>-0.4701718907987867</v>
       </c>
       <c r="I13">
-        <v>-0.396</v>
+        <v>-0.7522750252780587</v>
       </c>
       <c r="J13">
-        <v>-0.396</v>
+        <v>-0.7522750252780587</v>
       </c>
       <c r="K13">
-        <v>-1.14</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="L13">
-        <v>-0.7599999999999999</v>
+        <v>-0.08493427704752275</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -2005,31 +2011,31 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0.216</v>
+        <v>0.151</v>
       </c>
       <c r="V13">
-        <v>0.009863013698630137</v>
+        <v>0.01290598290598291</v>
       </c>
       <c r="W13">
-        <v>-0.06909090909090909</v>
+        <v>-0.005384615384615385</v>
       </c>
       <c r="X13">
-        <v>0.02430267097692251</v>
+        <v>0.05005596463140148</v>
       </c>
       <c r="Y13">
-        <v>-0.09339358006783161</v>
+        <v>-0.05544058001601686</v>
       </c>
       <c r="Z13">
-        <v>0.0940851784482218</v>
+        <v>0.06428757150286012</v>
       </c>
       <c r="AA13">
-        <v>-0.03725773066549583</v>
+        <v>-0.0483619344773791</v>
       </c>
       <c r="AB13">
-        <v>0.02430267097692251</v>
+        <v>0.05005596463140148</v>
       </c>
       <c r="AC13">
-        <v>-0.06156040164241833</v>
+        <v>-0.09841789910878057</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2041,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>-0.216</v>
+        <v>-0.151</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -2050,10 +2056,10 @@
         <v>0</v>
       </c>
       <c r="AJ13">
-        <v>-0.009961261759822912</v>
+        <v>-0.01307472508442289</v>
       </c>
       <c r="AK13">
-        <v>-0.01394988375096874</v>
+        <v>-0.00996765463066869</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2065,7 +2071,7 @@
         <v>-0</v>
       </c>
       <c r="AP13">
-        <v>0.3661016949152542</v>
+        <v>0.2029569892473118</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00459</v>
+        <v>0.063</v>
       </c>
       <c r="E2">
-        <v>0.00697</v>
+        <v>0.02935</v>
       </c>
       <c r="G2">
-        <v>0.4977739787769715</v>
+        <v>0.4071895118810722</v>
       </c>
       <c r="H2">
-        <v>0.4977739787769715</v>
+        <v>0.4071895118810722</v>
       </c>
       <c r="I2">
-        <v>0.2705077110053896</v>
+        <v>0.3329228608217254</v>
       </c>
       <c r="J2">
-        <v>0.2678178684572794</v>
+        <v>0.327977769114788</v>
       </c>
       <c r="K2">
-        <v>192.376</v>
+        <v>170.656</v>
       </c>
       <c r="L2">
-        <v>0.4080353109112158</v>
+        <v>0.3995224160131102</v>
       </c>
       <c r="M2">
-        <v>166.74</v>
+        <v>150.806</v>
       </c>
       <c r="N2">
-        <v>0.057177148343735</v>
+        <v>0.0532469458371584</v>
       </c>
       <c r="O2">
-        <v>0.8667401339044372</v>
+        <v>0.8836841365085318</v>
       </c>
       <c r="P2">
-        <v>126.01</v>
+        <v>128.36</v>
       </c>
       <c r="Q2">
-        <v>0.04321034222618476</v>
+        <v>0.0453216580749947</v>
       </c>
       <c r="R2">
-        <v>0.6550193371314509</v>
+        <v>0.7521563847740482</v>
       </c>
       <c r="S2">
-        <v>40.73</v>
+        <v>22.446</v>
       </c>
       <c r="T2">
-        <v>0.2442725200911599</v>
+        <v>0.1488402318210151</v>
       </c>
       <c r="U2">
-        <v>447.428</v>
+        <v>322.594</v>
       </c>
       <c r="V2">
-        <v>0.1534284342637679</v>
+        <v>0.1139022667890686</v>
       </c>
       <c r="W2">
-        <v>0.05144392209536602</v>
+        <v>0.05033474310842889</v>
       </c>
       <c r="X2">
-        <v>0.05217308890678861</v>
+        <v>0.05551360352376938</v>
       </c>
       <c r="Y2">
-        <v>-0.0007291668114225922</v>
+        <v>-0.005178860415340492</v>
       </c>
       <c r="Z2">
-        <v>0.1812051569420551</v>
+        <v>0.1663113189034627</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05157891833194144</v>
+        <v>0.05370746273926973</v>
       </c>
       <c r="AC2">
-        <v>-0.05157891833194144</v>
+        <v>-0.05466812193835843</v>
       </c>
       <c r="AD2">
-        <v>754.6800000000001</v>
+        <v>767.78</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>754.6800000000001</v>
+        <v>767.78</v>
       </c>
       <c r="AG2">
-        <v>307.2520000000001</v>
+        <v>445.186</v>
       </c>
       <c r="AH2">
-        <v>0.2055855816588938</v>
+        <v>0.2132734070744838</v>
       </c>
       <c r="AI2">
-        <v>0.2115976649899904</v>
+        <v>0.2182755836564814</v>
       </c>
       <c r="AJ2">
-        <v>0.0953176904759246</v>
+        <v>0.1358356934459353</v>
       </c>
       <c r="AK2">
-        <v>0.09850497827614688</v>
+        <v>0.1393433130321395</v>
       </c>
       <c r="AL2">
-        <v>7.315</v>
+        <v>17.277</v>
       </c>
       <c r="AM2">
-        <v>2.865</v>
+        <v>8.347000000000001</v>
       </c>
       <c r="AN2">
-        <v>4.253012183988369</v>
+        <v>3.940222830075388</v>
       </c>
       <c r="AO2">
-        <v>17.43485987696514</v>
+        <v>8.231058632864501</v>
       </c>
       <c r="AP2">
-        <v>1.731523956583975</v>
+        <v>2.284680560616247</v>
       </c>
       <c r="AQ2">
-        <v>44.5151832460733</v>
+        <v>17.03701928836708</v>
       </c>
     </row>
     <row r="3">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.5436893203883495</v>
+        <v>0.6960680127523912</v>
       </c>
       <c r="H3">
-        <v>0.5436893203883495</v>
+        <v>0.6960680127523912</v>
       </c>
       <c r="I3">
-        <v>0.6663724624889673</v>
+        <v>0.5494155154091392</v>
       </c>
       <c r="J3">
-        <v>0.6575789275723454</v>
+        <v>0.534001357893494</v>
       </c>
       <c r="K3">
-        <v>62.2</v>
+        <v>50.2</v>
       </c>
       <c r="L3">
-        <v>0.5489849955869374</v>
+        <v>0.5334750265674815</v>
       </c>
       <c r="M3">
-        <v>40.8</v>
+        <v>55</v>
       </c>
       <c r="N3">
-        <v>0.03036844064011909</v>
+        <v>0.04881512381290494</v>
       </c>
       <c r="O3">
-        <v>0.6559485530546623</v>
+        <v>1.095617529880478</v>
       </c>
       <c r="P3">
-        <v>40.8</v>
+        <v>55</v>
       </c>
       <c r="Q3">
-        <v>0.03036844064011909</v>
+        <v>0.04881512381290494</v>
       </c>
       <c r="R3">
-        <v>0.6559485530546623</v>
+        <v>1.095617529880478</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>17.5</v>
+        <v>9.98</v>
       </c>
       <c r="V3">
-        <v>0.01302567919612951</v>
+        <v>0.008857726102778024</v>
       </c>
       <c r="W3">
-        <v>0.3322649572649573</v>
+        <v>0.2486379395740466</v>
       </c>
       <c r="X3">
-        <v>0.05007711512095263</v>
+        <v>0.05231149116917512</v>
       </c>
       <c r="Y3">
-        <v>0.2821878421440047</v>
+        <v>0.1963264484048715</v>
       </c>
       <c r="Z3">
-        <v>3.058855291576676</v>
+        <v>0.6002423933150475</v>
       </c>
       <c r="AA3">
-        <v>2.011438782233984</v>
+        <v>0.3205302530954761</v>
       </c>
       <c r="AB3">
-        <v>0.05007151701315758</v>
+        <v>0.05229569308794073</v>
       </c>
       <c r="AC3">
-        <v>1.961367265220827</v>
+        <v>0.2682345600075353</v>
       </c>
       <c r="AD3">
-        <v>2.97</v>
+        <v>2.38</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.97</v>
+        <v>2.38</v>
       </c>
       <c r="AG3">
-        <v>-14.53</v>
+        <v>-7.600000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.002205767673991994</v>
+        <v>0.002107910865483402</v>
       </c>
       <c r="AI3">
-        <v>0.008782564982109589</v>
+        <v>0.007027282390457068</v>
       </c>
       <c r="AJ3">
-        <v>-0.01093327915603813</v>
+        <v>-0.006791171477079796</v>
       </c>
       <c r="AK3">
-        <v>-0.04531137929959148</v>
+        <v>-0.023121387283237</v>
       </c>
       <c r="AL3">
-        <v>0.129</v>
+        <v>0.107</v>
       </c>
       <c r="AM3">
-        <v>-4.321</v>
+        <v>-8.823</v>
       </c>
       <c r="AN3">
-        <v>0.03837209302325582</v>
+        <v>0.04541984732824427</v>
       </c>
       <c r="AO3">
-        <v>585.2713178294573</v>
+        <v>483.177570093458</v>
       </c>
       <c r="AP3">
-        <v>-0.1877260981912144</v>
+        <v>-0.1450381679389313</v>
       </c>
       <c r="AQ3">
-        <v>-17.4728072205508</v>
+        <v>-5.859684914428199</v>
       </c>
     </row>
     <row r="4">
@@ -850,121 +850,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.00459</v>
-      </c>
-      <c r="E4">
-        <v>-0.0449</v>
+        <v>0.198</v>
       </c>
       <c r="G4">
-        <v>0.8037676609105181</v>
+        <v>0.7676646706586826</v>
       </c>
       <c r="H4">
-        <v>0.8037676609105181</v>
+        <v>0.7676646706586826</v>
       </c>
       <c r="I4">
-        <v>0.4018838304552591</v>
+        <v>0.5580838323353293</v>
       </c>
       <c r="J4">
-        <v>0.3797009953691982</v>
+        <v>0.5313052875141436</v>
       </c>
       <c r="K4">
-        <v>23.2</v>
+        <v>42.1</v>
       </c>
       <c r="L4">
-        <v>0.3642072213500785</v>
+        <v>0.5041916167664671</v>
       </c>
       <c r="M4">
-        <v>16</v>
+        <v>16.76</v>
       </c>
       <c r="N4">
-        <v>0.05555555555555555</v>
+        <v>0.04456261632544535</v>
       </c>
       <c r="O4">
-        <v>0.6896551724137931</v>
+        <v>0.3980997624703087</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>15.6</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.04147833023132146</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.3705463182897862</v>
       </c>
       <c r="S4">
-        <v>16</v>
+        <v>1.159999999999998</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0.06921241050119323</v>
       </c>
       <c r="U4">
-        <v>52.5</v>
+        <v>62.2</v>
       </c>
       <c r="V4">
-        <v>0.1822916666666667</v>
+        <v>0.1653815474607817</v>
       </c>
       <c r="W4">
-        <v>0.08140350877192983</v>
+        <v>0.1458766458766459</v>
       </c>
       <c r="X4">
-        <v>0.05052769898244668</v>
+        <v>0.05340595460505592</v>
       </c>
       <c r="Y4">
-        <v>0.03087580978948315</v>
+        <v>0.09247069127158994</v>
       </c>
       <c r="Z4">
-        <v>0.2979447890064453</v>
+        <v>0.3339906482618487</v>
       </c>
       <c r="AA4">
-        <v>0.113129932950813</v>
+        <v>0.1774509974017968</v>
       </c>
       <c r="AB4">
-        <v>0.05069481330964262</v>
+        <v>0.05308154667303303</v>
       </c>
       <c r="AC4">
-        <v>0.06243511964117038</v>
+        <v>0.1243694507287637</v>
       </c>
       <c r="AD4">
-        <v>14.2</v>
+        <v>36.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>14.2</v>
+        <v>36.7</v>
       </c>
       <c r="AG4">
-        <v>-38.3</v>
+        <v>-25.5</v>
       </c>
       <c r="AH4">
-        <v>0.04698874917273329</v>
+        <v>0.08890503875968993</v>
       </c>
       <c r="AI4">
-        <v>0.04138735062663947</v>
+        <v>0.09478305785123968</v>
       </c>
       <c r="AJ4">
-        <v>-0.1533840608730477</v>
+        <v>-0.07273245864232743</v>
       </c>
       <c r="AK4">
-        <v>-0.1317962835512732</v>
+        <v>-0.07846153846153846</v>
       </c>
       <c r="AL4">
-        <v>0.026</v>
+        <v>1.87</v>
       </c>
       <c r="AM4">
-        <v>0.026</v>
+        <v>1.87</v>
       </c>
       <c r="AN4">
-        <v>0.2577132486388384</v>
+        <v>0.4711168164313222</v>
       </c>
       <c r="AO4">
-        <v>984.6153846153848</v>
+        <v>24.91978609625668</v>
       </c>
       <c r="AP4">
-        <v>-0.6950998185117967</v>
+        <v>-0.3273427471116816</v>
       </c>
       <c r="AQ4">
-        <v>984.6153846153848</v>
+        <v>24.91978609625668</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Securities House K.S.C.P. (KWSE:SECH)</t>
+          <t>Kuwait Investment Company K.S.C.P. (KWSE:KINV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -983,116 +980,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.00701</v>
+      </c>
+      <c r="E5">
+        <v>-0.0478</v>
+      </c>
       <c r="G5">
-        <v>0.492</v>
+        <v>0.4091415830546266</v>
       </c>
       <c r="H5">
-        <v>0.492</v>
+        <v>0.4091415830546266</v>
       </c>
       <c r="I5">
-        <v>0.2488</v>
+        <v>0.5039018952062431</v>
       </c>
       <c r="J5">
-        <v>0.2466569044414536</v>
+        <v>0.50360548232671</v>
       </c>
       <c r="K5">
-        <v>7.66</v>
+        <v>29.8</v>
       </c>
       <c r="L5">
-        <v>0.3064</v>
+        <v>0.3322185061315496</v>
       </c>
       <c r="M5">
-        <v>8.32</v>
+        <v>19.56</v>
       </c>
       <c r="N5">
-        <v>0.08648648648648649</v>
+        <v>0.09022140221402214</v>
       </c>
       <c r="O5">
-        <v>1.086161879895561</v>
+        <v>0.6563758389261746</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>8.56</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.03948339483394834</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.287248322147651</v>
       </c>
       <c r="S5">
-        <v>8.32</v>
+        <v>11</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0.5623721881390593</v>
       </c>
       <c r="U5">
-        <v>22.8</v>
+        <v>54.2</v>
       </c>
       <c r="V5">
-        <v>0.237006237006237</v>
+        <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.05144392209536602</v>
+        <v>0.08298524087997772</v>
       </c>
       <c r="X5">
-        <v>0.05064075996640922</v>
+        <v>0.0555181861254858</v>
       </c>
       <c r="Y5">
-        <v>0.0008031621289567997</v>
+        <v>0.02746705475449192</v>
       </c>
       <c r="Z5">
-        <v>0.2053050833538638</v>
+        <v>0.2525337837837838</v>
       </c>
       <c r="AA5">
-        <v>0.05063991632615864</v>
+        <v>0.1271773979862215</v>
       </c>
       <c r="AB5">
-        <v>0.05083910710935242</v>
+        <v>0.05425151918997567</v>
       </c>
       <c r="AC5">
-        <v>-0.0001991907831937756</v>
+        <v>0.07292587879624582</v>
       </c>
       <c r="AD5">
-        <v>5.88</v>
+        <v>61.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>5.88</v>
+        <v>61.1</v>
       </c>
       <c r="AG5">
-        <v>-16.92</v>
+        <v>6.899999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.05760188087774295</v>
+        <v>0.2198632601655272</v>
       </c>
       <c r="AI5">
-        <v>0.04236921746649373</v>
+        <v>0.113780260707635</v>
       </c>
       <c r="AJ5">
-        <v>-0.2134207870837538</v>
+        <v>0.0308448815377738</v>
       </c>
       <c r="AK5">
-        <v>-0.1458872219348163</v>
+        <v>0.01429163214581607</v>
       </c>
       <c r="AL5">
-        <v>0.193</v>
+        <v>13.9</v>
       </c>
       <c r="AM5">
-        <v>0.193</v>
+        <v>13.9</v>
       </c>
       <c r="AN5">
-        <v>0.760672703751617</v>
+        <v>0.9591836734693877</v>
       </c>
       <c r="AO5">
-        <v>32.2279792746114</v>
+        <v>3.251798561151079</v>
       </c>
       <c r="AP5">
-        <v>-2.188874514877102</v>
+        <v>0.108320251177394</v>
       </c>
       <c r="AQ5">
-        <v>32.2279792746114</v>
+        <v>3.251798561151079</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1106,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kuwait Investment Company K.S.C.P. (KWSE:KINV)</t>
+          <t>Arzan Financial Group for Financing and Investment - KPSC (KWSE:ARZAN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,121 +1115,109 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.09960000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="E6">
-        <v>-0.321</v>
+        <v>0.24</v>
       </c>
       <c r="G6">
-        <v>1.822742474916388</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>1.822742474916388</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.3193979933110369</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.3162932306944938</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>8.470000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="L6">
-        <v>0.1416387959866221</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="M6">
-        <v>44</v>
+        <v>11.15</v>
       </c>
       <c r="N6">
-        <v>0.1620029455081001</v>
+        <v>0.02002514367816092</v>
       </c>
       <c r="O6">
-        <v>5.194805194805195</v>
+        <v>0.637142857142857</v>
       </c>
       <c r="P6">
-        <v>44</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="Q6">
-        <v>0.1620029455081001</v>
+        <v>0.01681034482758621</v>
       </c>
       <c r="R6">
-        <v>5.194805194805195</v>
+        <v>0.5348571428571428</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.789999999999999</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.1605381165919282</v>
       </c>
       <c r="U6">
-        <v>64</v>
+        <v>15.8</v>
       </c>
       <c r="V6">
-        <v>0.235640648011782</v>
+        <v>0.0283764367816092</v>
       </c>
       <c r="W6">
-        <v>0.02060827250608273</v>
+        <v>0.0470051034112275</v>
       </c>
       <c r="X6">
-        <v>0.05217308890678861</v>
+        <v>0.05397148837833754</v>
       </c>
       <c r="Y6">
-        <v>-0.03156481640070588</v>
+        <v>-0.006966384967110037</v>
       </c>
       <c r="Z6">
-        <v>0.1467124631992149</v>
+        <v>0.05708294501397949</v>
       </c>
       <c r="AA6">
-        <v>0.04640415896842671</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05251935430579009</v>
+        <v>0.05279884322949133</v>
       </c>
       <c r="AC6">
-        <v>-0.006115195337363384</v>
+        <v>-0.05279884322949133</v>
       </c>
       <c r="AD6">
-        <v>60.1</v>
+        <v>81.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>60.1</v>
+        <v>81.8</v>
       </c>
       <c r="AG6">
-        <v>-3.899999999999999</v>
+        <v>66</v>
       </c>
       <c r="AH6">
-        <v>0.1811878203195658</v>
+        <v>0.1280927027873473</v>
       </c>
       <c r="AI6">
-        <v>0.1133962264150943</v>
+        <v>0.1379659301737224</v>
       </c>
       <c r="AJ6">
-        <v>-0.01456854688083675</v>
+        <v>0.1059730250481696</v>
       </c>
       <c r="AK6">
-        <v>-0.008369098712446349</v>
+        <v>0.1143649280887195</v>
       </c>
       <c r="AL6">
-        <v>6.79</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>6.79</v>
-      </c>
-      <c r="AN6">
-        <v>1.664819944598338</v>
-      </c>
-      <c r="AO6">
-        <v>2.812960235640648</v>
-      </c>
-      <c r="AP6">
-        <v>-0.1080332409972299</v>
-      </c>
-      <c r="AQ6">
-        <v>2.812960235640648</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Al Madar Finance and Investment Company K.S.C.P. (KWSE:MADAR)</t>
+          <t>Commercial Facilities Company S.A.K.P. (KWSE:FACIL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1246,115 +1237,109 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0808</v>
+        <v>-0.00646</v>
+      </c>
+      <c r="E7">
+        <v>-0.0219</v>
       </c>
       <c r="G7">
-        <v>0.2354260089686099</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0.2354260089686099</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0.4170403587443947</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0.4170403587443947</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>1.33</v>
+        <v>25</v>
       </c>
       <c r="L7">
-        <v>0.2982062780269059</v>
+        <v>0.5868544600938967</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>27.005</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.1029546321006481</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>1.0802</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>26.4</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.1006481128478841</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>1.056</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>0.6050000000000004</v>
+      </c>
+      <c r="T7">
+        <v>0.0224032586558045</v>
       </c>
       <c r="U7">
-        <v>0.577</v>
+        <v>58.3</v>
       </c>
       <c r="V7">
-        <v>0.007493506493506493</v>
+        <v>0.2222645825390774</v>
       </c>
       <c r="W7">
-        <v>0.01867977528089888</v>
+        <v>0.04891410682840931</v>
       </c>
       <c r="X7">
-        <v>0.05046973096762462</v>
+        <v>0.06742279400722473</v>
       </c>
       <c r="Y7">
-        <v>-0.03178995568672575</v>
+        <v>-0.01850868717881542</v>
       </c>
       <c r="Z7">
-        <v>0.06320861678004534</v>
+        <v>0.05427442986367691</v>
       </c>
       <c r="AA7">
-        <v>0.02636054421768708</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05034824766545265</v>
+        <v>0.05455975438441367</v>
       </c>
       <c r="AC7">
-        <v>-0.02398770344776557</v>
+        <v>-0.05455975438441367</v>
       </c>
       <c r="AD7">
-        <v>3.33</v>
+        <v>346.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3.33</v>
+        <v>346.3</v>
       </c>
       <c r="AG7">
-        <v>2.753</v>
+        <v>288</v>
       </c>
       <c r="AH7">
-        <v>0.04145400224075688</v>
+        <v>0.5690108445612883</v>
       </c>
       <c r="AI7">
-        <v>0.04181841014692955</v>
+        <v>0.4050292397660819</v>
       </c>
       <c r="AJ7">
-        <v>0.03451907765225132</v>
+        <v>0.5233508995093585</v>
       </c>
       <c r="AK7">
-        <v>0.0348247378341113</v>
+        <v>0.3614911509978662</v>
       </c>
       <c r="AL7">
-        <v>0.177</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>0.177</v>
-      </c>
-      <c r="AN7">
-        <v>1.790322580645161</v>
-      </c>
-      <c r="AO7">
-        <v>10.50847457627119</v>
-      </c>
-      <c r="AP7">
-        <v>1.48010752688172</v>
-      </c>
-      <c r="AQ7">
-        <v>10.50847457627119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1365,7 +1350,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arzan Financial Group for Financing and Investment - KPSC (KWSE:ARZAN)</t>
+          <t>KAMCO Investment Company K.S.C.P. (KWSE:KAMCO)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1374,10 +1359,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.262</v>
+        <v>0.163</v>
       </c>
       <c r="E8">
-        <v>0.5820000000000001</v>
+        <v>-0.248</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1392,85 +1377,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>35.5</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="L8">
-        <v>0.5599369085173501</v>
+        <v>0.01829745596868885</v>
       </c>
       <c r="M8">
-        <v>8.91</v>
+        <v>11</v>
       </c>
       <c r="N8">
-        <v>0.02961116650049851</v>
+        <v>0.1148225469728601</v>
       </c>
       <c r="O8">
-        <v>0.2509859154929577</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="P8">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="Q8">
-        <v>0.01927550681289465</v>
+        <v>0.1148225469728601</v>
       </c>
       <c r="R8">
-        <v>0.1633802816901408</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="S8">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.3490460157126824</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>26</v>
+        <v>87.2</v>
       </c>
       <c r="V8">
-        <v>0.08640744433366568</v>
+        <v>0.9102296450939458</v>
       </c>
       <c r="W8">
-        <v>0.08971443012383119</v>
+        <v>0.004717457114026237</v>
       </c>
       <c r="X8">
-        <v>0.05269189533180595</v>
+        <v>0.07125463452797372</v>
       </c>
       <c r="Y8">
-        <v>0.03702253479202524</v>
+        <v>-0.06653717741394748</v>
       </c>
       <c r="Z8">
-        <v>0.1432768361581921</v>
+        <v>0.2115066225165563</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05157891833194144</v>
+        <v>0.0547764894923032</v>
       </c>
       <c r="AC8">
-        <v>-0.05157891833194144</v>
+        <v>-0.0547764894923032</v>
       </c>
       <c r="AD8">
-        <v>82.90000000000001</v>
+        <v>158.5</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>82.90000000000001</v>
+        <v>158.5</v>
       </c>
       <c r="AG8">
-        <v>56.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="AH8">
-        <v>0.2159979155810318</v>
+        <v>0.6232795910342115</v>
       </c>
       <c r="AI8">
-        <v>0.1404846636163362</v>
+        <v>0.438208460049765</v>
       </c>
       <c r="AJ8">
-        <v>0.1590273896031303</v>
+        <v>0.4266906044284859</v>
       </c>
       <c r="AK8">
-        <v>0.1008686403120014</v>
+        <v>0.2597449908925319</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1487,7 +1472,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Al Manar Financing and Leasing Company K.S.C. (Public) (KWSE:ALMANAR)</t>
+          <t>KFIC Invest (K.S.C.P) (KWSE:KFIC)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1495,6 +1480,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D9">
+        <v>-0.0227</v>
+      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1508,85 +1496,82 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>4.07</v>
+        <v>-4.63</v>
       </c>
       <c r="L9">
-        <v>0.5012315270935962</v>
+        <v>-0.4171171171171171</v>
       </c>
       <c r="M9">
-        <v>13.41</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.2655445544554456</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>3.294840294840295</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>0.11</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.002178217821782178</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.02702702702702703</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>13.3</v>
-      </c>
-      <c r="T9">
-        <v>0.9917971662938107</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>17.1</v>
+        <v>13.7</v>
       </c>
       <c r="V9">
-        <v>0.3386138613861386</v>
+        <v>0.202962962962963</v>
       </c>
       <c r="W9">
-        <v>0.03998035363457761</v>
+        <v>-0.03442379182156134</v>
       </c>
       <c r="X9">
-        <v>0.05352302462826188</v>
+        <v>0.0559218453988108</v>
       </c>
       <c r="Y9">
-        <v>-0.01354267099368427</v>
+        <v>-0.09034563722037214</v>
       </c>
       <c r="Z9">
-        <v>0.07883495145631067</v>
+        <v>0.08072727272727273</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05367228391912036</v>
+        <v>0.05498396041232601</v>
       </c>
       <c r="AC9">
-        <v>-0.05367228391912036</v>
+        <v>-0.05498396041232601</v>
       </c>
       <c r="AD9">
-        <v>18.3</v>
+        <v>21.4</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>18.3</v>
+        <v>21.4</v>
       </c>
       <c r="AG9">
-        <v>1.199999999999999</v>
+        <v>7.699999999999999</v>
       </c>
       <c r="AH9">
-        <v>0.2659883720930233</v>
+        <v>0.2407199100112486</v>
       </c>
       <c r="AI9">
-        <v>0.1716697936210131</v>
+        <v>0.1399607586657946</v>
       </c>
       <c r="AJ9">
-        <v>0.02321083172147</v>
+        <v>0.1023936170212766</v>
       </c>
       <c r="AK9">
-        <v>0.01340782122905027</v>
+        <v>0.05531609195402299</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1603,7 +1588,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KAMCO Investment Company K.S.C.P. (KWSE:KAMCO)</t>
+          <t>Credit Rating And Collection Company K.S.C. (Public) (KWSE:TAHSSILAT)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1612,109 +1597,109 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.224</v>
-      </c>
-      <c r="E10">
-        <v>0.338</v>
+        <v>0.111</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>-0.4654135338345864</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>-0.4654135338345864</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>-0.03157894736842105</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>-0.03157894736842105</v>
       </c>
       <c r="K10">
-        <v>19.1</v>
+        <v>0.841</v>
       </c>
       <c r="L10">
-        <v>0.2630853994490359</v>
+        <v>0.6323308270676691</v>
       </c>
       <c r="M10">
-        <v>10.8</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.09391304347826088</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.5654450261780105</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>10.8</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.09391304347826088</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.5654450261780105</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>101.6</v>
+        <v>0.314</v>
       </c>
       <c r="V10">
-        <v>0.8834782608695652</v>
+        <v>0.02778761061946903</v>
       </c>
       <c r="W10">
-        <v>0.09720101781170484</v>
+        <v>0.05532894736842105</v>
       </c>
       <c r="X10">
-        <v>0.06211942237766437</v>
+        <v>0.05228727464604656</v>
       </c>
       <c r="Y10">
-        <v>0.03508159543404048</v>
+        <v>0.003041672722374496</v>
       </c>
       <c r="Z10">
-        <v>0.3007456503728252</v>
+        <v>0.08837796531330987</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>-0.002790883115157153</v>
       </c>
       <c r="AB10">
-        <v>0.05398813018715677</v>
+        <v>0.05228727464604656</v>
       </c>
       <c r="AC10">
-        <v>-0.05398813018715677</v>
+        <v>-0.05507815776120371</v>
       </c>
       <c r="AD10">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>43.40000000000001</v>
+        <v>-0.314</v>
       </c>
       <c r="AH10">
-        <v>0.5576923076923077</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.4087961657738934</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>0.273989898989899</v>
+        <v>-0.02858183142180958</v>
       </c>
       <c r="AK10">
-        <v>0.1714737258000791</v>
+        <v>-0.01976583154979227</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
         <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>-0</v>
+      </c>
+      <c r="AP10">
+        <v>8.051282051282051</v>
       </c>
     </row>
     <row r="11">
@@ -1725,7 +1710,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Commercial Facilities Company S.A.K.P. (KWSE:FACIL)</t>
+          <t>Al Manar Financing and Leasing Company K.S.C. (Public) (KWSE:ALMANAR)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1734,10 +1719,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0064</v>
+        <v>-0.008</v>
       </c>
       <c r="E11">
-        <v>0.00697</v>
+        <v>0.0806</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1752,85 +1737,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>33.1</v>
+        <v>4.57</v>
       </c>
       <c r="L11">
-        <v>0.7164502164502164</v>
+        <v>0.4851380042462846</v>
       </c>
       <c r="M11">
-        <v>24.5</v>
+        <v>3.081</v>
       </c>
       <c r="N11">
-        <v>0.08265856950067477</v>
+        <v>0.06313524590163935</v>
       </c>
       <c r="O11">
-        <v>0.7401812688821752</v>
+        <v>0.67417943107221</v>
       </c>
       <c r="P11">
-        <v>24.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q11">
-        <v>0.08265856950067477</v>
+        <v>0.05</v>
       </c>
       <c r="R11">
-        <v>0.7401812688821752</v>
+        <v>0.5339168490153172</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>0.641</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.2080493346316131</v>
       </c>
       <c r="U11">
-        <v>120.7</v>
+        <v>7.5</v>
       </c>
       <c r="V11">
-        <v>0.4072199730094467</v>
+        <v>0.1536885245901639</v>
       </c>
       <c r="W11">
-        <v>0.0625354241450973</v>
+        <v>0.05175537938844848</v>
       </c>
       <c r="X11">
-        <v>0.06279012907143083</v>
+        <v>0.0616606541464701</v>
       </c>
       <c r="Y11">
-        <v>-0.0002547049263335321</v>
+        <v>-0.009905274758021623</v>
       </c>
       <c r="Z11">
-        <v>0.05750560119492159</v>
+        <v>0.1052513966480447</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.05408191999251287</v>
+        <v>0.0563060355430255</v>
       </c>
       <c r="AC11">
-        <v>-0.05408191999251287</v>
+        <v>-0.0563060355430255</v>
       </c>
       <c r="AD11">
-        <v>394.5</v>
+        <v>39.9</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>394.5</v>
+        <v>39.9</v>
       </c>
       <c r="AG11">
-        <v>273.8</v>
+        <v>32.4</v>
       </c>
       <c r="AH11">
-        <v>0.5709943551888841</v>
+        <v>0.4498308906426156</v>
       </c>
       <c r="AI11">
-        <v>0.4355266063148598</v>
+        <v>0.3059815950920245</v>
       </c>
       <c r="AJ11">
-        <v>0.4801823921431077</v>
+        <v>0.3990147783251232</v>
       </c>
       <c r="AK11">
-        <v>0.3487453827537894</v>
+        <v>0.2636289666395443</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1847,7 +1832,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KFIC Invest (K.S.C.P) (KWSE:KFIC)</t>
+          <t>The Securities House K.S.C.P. (KWSE:SECH)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1856,34 +1841,37 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0127</v>
+        <v>0.445</v>
+      </c>
+      <c r="E12">
+        <v>0.109</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>-0.06313131313131314</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>-0.06313131313131314</v>
       </c>
       <c r="K12">
-        <v>-2.17</v>
+        <v>4.34</v>
       </c>
       <c r="L12">
-        <v>-0.1561151079136691</v>
+        <v>0.2191919191919192</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>7.25</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.1034236804564907</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.670506912442396</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1892,186 +1880,82 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>7.25</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>24.5</v>
+        <v>13.4</v>
       </c>
       <c r="V12">
-        <v>0.3746177370030581</v>
+        <v>0.1911554921540656</v>
       </c>
       <c r="W12">
-        <v>-0.01519607843137255</v>
+        <v>0.03255813953488372</v>
       </c>
       <c r="X12">
-        <v>0.05407902538459734</v>
+        <v>0.05550902092205297</v>
       </c>
       <c r="Y12">
-        <v>-0.06927510381596989</v>
+        <v>-0.02295088138716925</v>
       </c>
       <c r="Z12">
-        <v>0.09559834938101788</v>
+        <v>0.1822365393465255</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>-0.01150483202945237</v>
       </c>
       <c r="AB12">
-        <v>0.05503668518547522</v>
+        <v>0.05316340628856378</v>
       </c>
       <c r="AC12">
-        <v>-0.05503668518547522</v>
+        <v>-0.06466823831801614</v>
       </c>
       <c r="AD12">
-        <v>27.5</v>
+        <v>19.7</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>27.5</v>
+        <v>19.7</v>
       </c>
       <c r="AG12">
-        <v>3</v>
+        <v>6.299999999999999</v>
       </c>
       <c r="AH12">
-        <v>0.2960172228202368</v>
+        <v>0.2193763919821826</v>
       </c>
       <c r="AI12">
-        <v>0.1672749391727494</v>
+        <v>0.1353951890034364</v>
       </c>
       <c r="AJ12">
-        <v>0.04385964912280702</v>
+        <v>0.08246073298429318</v>
       </c>
       <c r="AK12">
-        <v>0.02144388849177984</v>
+        <v>0.04769114307342921</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Kuwait</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Credit Rating And Collection Company K.S.C. (Public) (KWSE:TAHSSILAT)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G13">
-        <v>-0.4701718907987867</v>
-      </c>
-      <c r="H13">
-        <v>-0.4701718907987867</v>
-      </c>
-      <c r="I13">
-        <v>-0.7522750252780587</v>
-      </c>
-      <c r="J13">
-        <v>-0.7522750252780587</v>
-      </c>
-      <c r="K13">
-        <v>-0.08400000000000001</v>
-      </c>
-      <c r="L13">
-        <v>-0.08493427704752275</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0.151</v>
-      </c>
-      <c r="V13">
-        <v>0.01290598290598291</v>
-      </c>
-      <c r="W13">
-        <v>-0.005384615384615385</v>
-      </c>
-      <c r="X13">
-        <v>0.05005596463140148</v>
-      </c>
-      <c r="Y13">
-        <v>-0.05544058001601686</v>
-      </c>
-      <c r="Z13">
-        <v>0.06428757150286012</v>
-      </c>
-      <c r="AA13">
-        <v>-0.0483619344773791</v>
-      </c>
-      <c r="AB13">
-        <v>0.05005596463140148</v>
-      </c>
-      <c r="AC13">
-        <v>-0.09841789910878057</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>-0.151</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>-0.01307472508442289</v>
-      </c>
-      <c r="AK13">
-        <v>-0.00996765463066869</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>-0</v>
-      </c>
-      <c r="AP13">
-        <v>0.2029569892473118</v>
+        <v>1.4</v>
+      </c>
+      <c r="AN12">
+        <v>21.98660714285714</v>
+      </c>
+      <c r="AO12">
+        <v>-0.8928571428571429</v>
+      </c>
+      <c r="AP12">
+        <v>7.031249999999998</v>
+      </c>
+      <c r="AQ12">
+        <v>-0.8928571428571429</v>
       </c>
     </row>
   </sheetData>
